--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -939,7 +939,7 @@
         <v>0.05200000000000002</v>
       </c>
       <c r="H11">
-        <v>0.04327339885162032</v>
+        <v>0.04327339885162035</v>
       </c>
       <c r="I11">
         <v>0.02820962773999661</v>
@@ -960,7 +960,7 @@
         <v>0.04500000000000004</v>
       </c>
       <c r="O11">
-        <v>0.03627339885162034</v>
+        <v>0.03627339885162037</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -1080,7 +1080,7 @@
         <v>0.01862500000000003</v>
       </c>
       <c r="H14">
-        <v>0.008256875250248874</v>
+        <v>0.008256875250248846</v>
       </c>
       <c r="I14">
         <v>0.01001663639923409</v>
@@ -1101,7 +1101,7 @@
         <v>0.0172500000000001</v>
       </c>
       <c r="O14">
-        <v>0.006881875250248942</v>
+        <v>0.006881875250248914</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
